--- a/Data/uncertainty/wt.xlsx
+++ b/Data/uncertainty/wt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,13 +77,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -551,148 +544,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1048,15 +1041,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16.5309734513274" customWidth="1"/>
     <col min="3" max="3" width="15.2743362831858" customWidth="1"/>
     <col min="4" max="4" width="17.1946902654867" customWidth="1"/>
+    <col min="9" max="9" width="12.7964601769912"/>
+    <col min="13" max="13" width="12.7964601769912"/>
+    <col min="15" max="15" width="12.7964601769912"/>
+    <col min="17" max="17" width="12.7964601769912"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="2:18">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,27 +1064,31 @@
         <v>2</v>
       </c>
       <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1108,30 +1109,46 @@
         <v>188.943137254902</v>
       </c>
       <c r="I2" s="2">
+        <f ca="1">H2*2</f>
+        <v>377.886274509804</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.969885</v>
       </c>
-      <c r="J2" s="2">
-        <f ca="1" t="shared" ref="J2:J25" si="0">H2*I2</f>
+      <c r="K2" s="2">
+        <f ca="1" t="shared" ref="K2:K25" si="0">H2*J2</f>
         <v>183.253114676471</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C1)-1)*4,0)</f>
         <v>119.718944511216</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
+        <f ca="1">L2*2</f>
+        <v>239.437889022432</v>
+      </c>
+      <c r="N2" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D1)-1)*4,0)</f>
         <v>258.167329998588</v>
       </c>
-      <c r="M2" s="2">
-        <f ca="1" t="shared" ref="M2:M25" si="1">IF(OR(J2&gt;K2,J2&lt;L2),J2,H2)</f>
+      <c r="O2" s="2">
+        <f ca="1">N2*2</f>
+        <v>516.334659997176</v>
+      </c>
+      <c r="P2" s="2">
+        <f ca="1" t="shared" ref="P2:P25" si="1">IF(OR(K2&gt;L2,K2&lt;N2),K2,H2)</f>
         <v>183.253114676471</v>
       </c>
-      <c r="N2" s="2">
-        <f ca="1" t="shared" ref="N2:N25" si="2">IF(H2=M2,0,1)</f>
+      <c r="Q2" s="2">
+        <f ca="1">P2*2</f>
+        <v>366.506229352941</v>
+      </c>
+      <c r="R2" s="2">
+        <f ca="1" t="shared" ref="R2:R25" si="2">IF(H2=P2,0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1152,30 +1169,46 @@
         <v>178.809803921569</v>
       </c>
       <c r="I3" s="2">
+        <f ca="1" t="shared" ref="I3:I25" si="3">H3*2</f>
+        <v>357.619607843138</v>
+      </c>
+      <c r="J3" s="2">
         <v>1.021257</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>182.610763923529</v>
-      </c>
-      <c r="K3" s="2">
+        <v>182.61076392353</v>
+      </c>
+      <c r="L3" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C2)-1)*4,0)</f>
         <v>124.149560756958</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
+        <f ca="1" t="shared" ref="M3:M25" si="4">L3*2</f>
+        <v>248.299121513916</v>
+      </c>
+      <c r="N3" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D2)-1)*4,0)</f>
         <v>233.470047086179</v>
       </c>
-      <c r="M3" s="2">
+      <c r="O3" s="2">
+        <f ca="1" t="shared" ref="O3:O25" si="5">N3*2</f>
+        <v>466.940094172358</v>
+      </c>
+      <c r="P3" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>182.610763923529</v>
-      </c>
-      <c r="N3" s="2">
+        <v>182.61076392353</v>
+      </c>
+      <c r="Q3" s="2">
+        <f ca="1" t="shared" ref="Q3:Q25" si="6">P3*2</f>
+        <v>365.22152784706</v>
+      </c>
+      <c r="R3" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1196,30 +1229,46 @@
         <v>184.441176470588</v>
       </c>
       <c r="I4" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>368.882352941176</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.997038</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>183.894861705882</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C3)-1)*4,0)</f>
         <v>115.196850610752</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>230.393701221504</v>
+      </c>
+      <c r="N4" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D3)-1)*4,0)</f>
         <v>253.685502330424</v>
       </c>
-      <c r="M4" s="2">
+      <c r="O4" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>507.371004660848</v>
+      </c>
+      <c r="P4" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>183.894861705882</v>
       </c>
-      <c r="N4" s="2">
+      <c r="Q4" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>367.789723411764</v>
+      </c>
+      <c r="R4" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1240,30 +1289,46 @@
         <v>181.903921568628</v>
       </c>
       <c r="I5" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>363.807843137256</v>
+      </c>
+      <c r="J5" s="2">
         <v>1.03662</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>188.565243176471</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C4)-1)*4,0)</f>
         <v>126.55010187503</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>253.10020375006</v>
+      </c>
+      <c r="N5" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D4)-1)*4,0)</f>
         <v>237.257741262225</v>
       </c>
-      <c r="M5" s="2">
+      <c r="O5" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>474.51548252445</v>
+      </c>
+      <c r="P5" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>188.565243176471</v>
       </c>
-      <c r="N5" s="2">
+      <c r="Q5" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>377.130486352942</v>
+      </c>
+      <c r="R5" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1284,30 +1349,46 @@
         <v>204.531372549019</v>
       </c>
       <c r="I6" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>409.062745098038</v>
+      </c>
+      <c r="J6" s="2">
         <v>1.034074</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>211.500574537255</v>
-      </c>
-      <c r="K6" s="2">
+        <v>211.500574537254</v>
+      </c>
+      <c r="L6" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C5)-1)*4,0)</f>
         <v>163.109180408452</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>326.218360816904</v>
+      </c>
+      <c r="N6" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D5)-1)*4,0)</f>
         <v>245.953564689587</v>
       </c>
-      <c r="M6" s="2">
+      <c r="O6" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>491.907129379174</v>
+      </c>
+      <c r="P6" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>211.500574537255</v>
-      </c>
-      <c r="N6" s="2">
+        <v>211.500574537254</v>
+      </c>
+      <c r="Q6" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>423.001149074509</v>
+      </c>
+      <c r="R6" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1328,30 +1409,46 @@
         <v>182.105882352941</v>
       </c>
       <c r="I7" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>364.211764705882</v>
+      </c>
+      <c r="J7" s="2">
         <v>0.988478</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>180.007658376471</v>
-      </c>
-      <c r="K7" s="2">
+        <v>180.00765837647</v>
+      </c>
+      <c r="L7" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C6)-1)*4,0)</f>
         <v>132.246701298601</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>264.493402597202</v>
+      </c>
+      <c r="N7" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D6)-1)*4,0)</f>
         <v>231.965063407281</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>463.930126814562</v>
+      </c>
+      <c r="P7" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>180.007658376471</v>
-      </c>
-      <c r="N7" s="2">
+        <v>180.00765837647</v>
+      </c>
+      <c r="Q7" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>360.015316752941</v>
+      </c>
+      <c r="R7" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1372,30 +1469,46 @@
         <v>177.550980392157</v>
       </c>
       <c r="I8" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>355.101960784314</v>
+      </c>
+      <c r="J8" s="2">
         <v>1.00025</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>177.595368137255</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C7)-1)*4,0)</f>
         <v>105.356974899556</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>210.713949799112</v>
+      </c>
+      <c r="N8" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D7)-1)*4,0)</f>
         <v>249.744985884758</v>
       </c>
-      <c r="M8" s="2">
+      <c r="O8" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>499.489971769516</v>
+      </c>
+      <c r="P8" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>177.595368137255</v>
       </c>
-      <c r="N8" s="2">
+      <c r="Q8" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>355.19073627451</v>
+      </c>
+      <c r="R8" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1416,30 +1529,46 @@
         <v>185.919607843137</v>
       </c>
       <c r="I9" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>371.839215686274</v>
+      </c>
+      <c r="J9" s="2">
         <v>1.037387</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>192.870584221569</v>
-      </c>
-      <c r="K9" s="2">
+        <v>192.870584221568</v>
+      </c>
+      <c r="L9" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C8)-1)*4,0)</f>
         <v>111.784480216538</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>223.568960433076</v>
+      </c>
+      <c r="N9" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D8)-1)*4,0)</f>
         <v>260.054735469737</v>
       </c>
-      <c r="M9" s="2">
+      <c r="O9" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>520.109470939474</v>
+      </c>
+      <c r="P9" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>192.870584221569</v>
-      </c>
-      <c r="N9" s="2">
+        <v>192.870584221568</v>
+      </c>
+      <c r="Q9" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>385.741168443137</v>
+      </c>
+      <c r="R9" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1460,30 +1589,46 @@
         <v>205.854901960784</v>
       </c>
       <c r="I10" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>411.709803921568</v>
+      </c>
+      <c r="J10" s="2">
         <v>1.045036</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>215.12578332549</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C9)-1)*4,0)</f>
         <v>129.951824858402</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>259.903649716804</v>
+      </c>
+      <c r="N10" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D9)-1)*4,0)</f>
         <v>281.757979063166</v>
       </c>
-      <c r="M10" s="2">
+      <c r="O10" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>563.515958126332</v>
+      </c>
+      <c r="P10" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>215.12578332549</v>
       </c>
-      <c r="N10" s="2">
+      <c r="Q10" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>430.25156665098</v>
+      </c>
+      <c r="R10" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1504,30 +1649,46 @@
         <v>221.33137254902</v>
       </c>
       <c r="I11" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>442.66274509804</v>
+      </c>
+      <c r="J11" s="2">
         <v>0.986436</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>218.329233811765</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C10)-1)*4,0)</f>
         <v>157.557620138331</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>315.115240276662</v>
+      </c>
+      <c r="N11" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D10)-1)*4,0)</f>
         <v>285.105124959708</v>
       </c>
-      <c r="M11" s="2">
+      <c r="O11" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>570.210249919416</v>
+      </c>
+      <c r="P11" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>218.329233811765</v>
       </c>
-      <c r="N11" s="2">
+      <c r="Q11" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>436.65846762353</v>
+      </c>
+      <c r="R11" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1548,30 +1709,46 @@
         <v>208.882352941177</v>
       </c>
       <c r="I12" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>417.764705882354</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.972533</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>203.144981352941</v>
-      </c>
-      <c r="K12" s="2">
+        <v>203.144981352942</v>
+      </c>
+      <c r="L12" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C11)-1)*4,0)</f>
         <v>138.602670671635</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>277.20534134327</v>
+      </c>
+      <c r="N12" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D11)-1)*4,0)</f>
         <v>279.162035210718</v>
       </c>
-      <c r="M12" s="2">
+      <c r="O12" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>558.324070421436</v>
+      </c>
+      <c r="P12" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>203.144981352941</v>
-      </c>
-      <c r="N12" s="2">
+        <v>203.144981352942</v>
+      </c>
+      <c r="Q12" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>406.289962705883</v>
+      </c>
+      <c r="R12" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1592,30 +1769,46 @@
         <v>179.886274509804</v>
       </c>
       <c r="I13" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>359.772549019608</v>
+      </c>
+      <c r="J13" s="2">
         <v>1.006938</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>181.134325482353</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C12)-1)*4,0)</f>
         <v>130.515331171276</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>261.030662342552</v>
+      </c>
+      <c r="N13" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D12)-1)*4,0)</f>
         <v>229.257217848332</v>
       </c>
-      <c r="M13" s="2">
+      <c r="O13" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>458.514435696664</v>
+      </c>
+      <c r="P13" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>181.134325482353</v>
       </c>
-      <c r="N13" s="2">
+      <c r="Q13" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>362.268650964706</v>
+      </c>
+      <c r="R13" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1636,30 +1829,46 @@
         <v>167.398039215686</v>
       </c>
       <c r="I14" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>334.796078431372</v>
+      </c>
+      <c r="J14" s="2">
         <v>1.024603</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>171.51653317451</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C13)-1)*4,0)</f>
         <v>135.810048016425</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>271.62009603285</v>
+      </c>
+      <c r="N14" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D13)-1)*4,0)</f>
         <v>198.986030414947</v>
       </c>
-      <c r="M14" s="2">
+      <c r="O14" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>397.972060829894</v>
+      </c>
+      <c r="P14" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>171.51653317451</v>
       </c>
-      <c r="N14" s="2">
+      <c r="Q14" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>343.033066349019</v>
+      </c>
+      <c r="R14" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1680,30 +1889,46 @@
         <v>197.852941176471</v>
       </c>
       <c r="I15" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>395.705882352942</v>
+      </c>
+      <c r="J15" s="2">
         <v>0.985</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>194.885147058824</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C14)-1)*4,0)</f>
         <v>155.3837667934</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>310.7675335868</v>
+      </c>
+      <c r="N15" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D14)-1)*4,0)</f>
         <v>240.322115559542</v>
       </c>
-      <c r="M15" s="2">
+      <c r="O15" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>480.644231119084</v>
+      </c>
+      <c r="P15" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>194.885147058824</v>
       </c>
-      <c r="N15" s="2">
+      <c r="Q15" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>389.770294117648</v>
+      </c>
+      <c r="R15" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1724,30 +1949,46 @@
         <v>249.780392156863</v>
       </c>
       <c r="I16" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>499.560784313726</v>
+      </c>
+      <c r="J16" s="2">
         <v>0.989829</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>247.239875788235</v>
-      </c>
-      <c r="K16" s="2">
+        <v>247.239875788236</v>
+      </c>
+      <c r="L16" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C15)-1)*4,0)</f>
         <v>193.38840209909</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>386.77680419818</v>
+      </c>
+      <c r="N16" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D15)-1)*4,0)</f>
         <v>306.172382214635</v>
       </c>
-      <c r="M16" s="2">
+      <c r="O16" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>612.34476442927</v>
+      </c>
+      <c r="P16" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>247.239875788235</v>
-      </c>
-      <c r="N16" s="2">
+        <v>247.239875788236</v>
+      </c>
+      <c r="Q16" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>494.479751576471</v>
+      </c>
+      <c r="R16" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1768,30 +2009,46 @@
         <v>233.178431372549</v>
       </c>
       <c r="I17" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>466.356862745098</v>
+      </c>
+      <c r="J17" s="2">
         <v>0.997796</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>232.664506109804</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C16)-1)*4,0)</f>
         <v>161.7657411752</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>323.5314823504</v>
+      </c>
+      <c r="N17" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D16)-1)*4,0)</f>
         <v>304.591121569898</v>
       </c>
-      <c r="M17" s="2">
+      <c r="O17" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>609.182243139796</v>
+      </c>
+      <c r="P17" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>232.664506109804</v>
       </c>
-      <c r="N17" s="2">
+      <c r="Q17" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>465.329012219608</v>
+      </c>
+      <c r="R17" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1812,30 +2069,46 @@
         <v>240.337254901961</v>
       </c>
       <c r="I18" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>480.674509803922</v>
+      </c>
+      <c r="J18" s="2">
         <v>0.964075</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>231.703139019608</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C17)-1)*4,0)</f>
         <v>176.293611131624</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>352.587222263248</v>
+      </c>
+      <c r="N18" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D17)-1)*4,0)</f>
         <v>304.380898672297</v>
       </c>
-      <c r="M18" s="2">
+      <c r="O18" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>608.761797344594</v>
+      </c>
+      <c r="P18" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>231.703139019608</v>
       </c>
-      <c r="N18" s="2">
+      <c r="Q18" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>463.406278039216</v>
+      </c>
+      <c r="R18" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1856,30 +2129,46 @@
         <v>242.305882352941</v>
       </c>
       <c r="I19" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>484.611764705882</v>
+      </c>
+      <c r="J19" s="2">
         <v>0.964811</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>233.779380658823</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C18)-1)*4,0)</f>
         <v>166.827227346431</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>333.654454692862</v>
+      </c>
+      <c r="N19" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D18)-1)*4,0)</f>
         <v>317.784537359451</v>
       </c>
-      <c r="M19" s="2">
+      <c r="O19" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>635.569074718902</v>
+      </c>
+      <c r="P19" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>233.779380658823</v>
       </c>
-      <c r="N19" s="2">
+      <c r="Q19" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>467.558761317647</v>
+      </c>
+      <c r="R19" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1900,30 +2189,46 @@
         <v>216.007843137255</v>
       </c>
       <c r="I20" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>432.01568627451</v>
+      </c>
+      <c r="J20" s="2">
         <v>1.033227</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>223.185135741177</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C19)-1)*4,0)</f>
         <v>144.139819550251</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>288.279639100502</v>
+      </c>
+      <c r="N20" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D19)-1)*4,0)</f>
         <v>287.875866724259</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O20" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>575.751733448518</v>
+      </c>
+      <c r="P20" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>223.185135741177</v>
       </c>
-      <c r="N20" s="2">
+      <c r="Q20" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>446.370271482353</v>
+      </c>
+      <c r="R20" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1944,30 +2249,46 @@
         <v>193.172549019608</v>
       </c>
       <c r="I21" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>386.345098039216</v>
+      </c>
+      <c r="J21" s="2">
         <v>1.031367</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>199.231792364706</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C20)-1)*4,0)</f>
         <v>115.369477089702</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>230.738954179404</v>
+      </c>
+      <c r="N21" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D20)-1)*4,0)</f>
         <v>270.975620949514</v>
       </c>
-      <c r="M21" s="2">
+      <c r="O21" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>541.951241899028</v>
+      </c>
+      <c r="P21" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>199.231792364706</v>
       </c>
-      <c r="N21" s="2">
+      <c r="Q21" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>398.463584729412</v>
+      </c>
+      <c r="R21" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1988,30 +2309,46 @@
         <v>219.188235294118</v>
       </c>
       <c r="I22" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>438.376470588236</v>
+      </c>
+      <c r="J22" s="2">
         <v>0.963888</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>211.272909741177</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C21)-1)*4,0)</f>
         <v>143.36330421594</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>286.72660843188</v>
+      </c>
+      <c r="N22" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D21)-1)*4,0)</f>
         <v>295.013166372296</v>
       </c>
-      <c r="M22" s="2">
+      <c r="O22" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>590.026332744592</v>
+      </c>
+      <c r="P22" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>211.272909741177</v>
       </c>
-      <c r="N22" s="2">
+      <c r="Q22" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>422.545819482354</v>
+      </c>
+      <c r="R22" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2032,30 +2369,46 @@
         <v>219.890196078431</v>
       </c>
       <c r="I23" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>439.780392156862</v>
+      </c>
+      <c r="J23" s="2">
         <v>0.956548</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>210.335527278431</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C22)-1)*4,0)</f>
         <v>148.981668733066</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>297.963337466132</v>
+      </c>
+      <c r="N23" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D22)-1)*4,0)</f>
         <v>290.798723423796</v>
       </c>
-      <c r="M23" s="2">
+      <c r="O23" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>581.597446847592</v>
+      </c>
+      <c r="P23" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>210.335527278431</v>
       </c>
-      <c r="N23" s="2">
+      <c r="Q23" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>420.671054556862</v>
+      </c>
+      <c r="R23" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2076,30 +2429,46 @@
         <v>165.135294117647</v>
       </c>
       <c r="I24" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>330.270588235294</v>
+      </c>
+      <c r="J24" s="2">
         <v>0.971773</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>160.474020170588</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C23)-1)*4,0)</f>
         <v>91.2038401770119</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>182.407680354024</v>
+      </c>
+      <c r="N24" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D23)-1)*4,0)</f>
         <v>239.066748058282</v>
       </c>
-      <c r="M24" s="2">
+      <c r="O24" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>478.133496116564</v>
+      </c>
+      <c r="P24" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>160.474020170588</v>
       </c>
-      <c r="N24" s="2">
+      <c r="Q24" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>320.948040341176</v>
+      </c>
+      <c r="R24" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2120,25 +2489,41 @@
         <v>181.705882352941</v>
       </c>
       <c r="I25" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>363.411764705882</v>
+      </c>
+      <c r="J25" s="2">
         <v>0.975908</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>177.328224235294</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C24)-1)*4,0)</f>
         <v>99.5708208356463</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>199.141641671293</v>
+      </c>
+      <c r="N25" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D24)-1)*4,0)</f>
         <v>263.840943870236</v>
       </c>
-      <c r="M25" s="2">
+      <c r="O25" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>527.681887740472</v>
+      </c>
+      <c r="P25" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>177.328224235294</v>
       </c>
-      <c r="N25" s="2">
+      <c r="Q25" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>354.656448470588</v>
+      </c>
+      <c r="R25" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
